--- a/data/nzd0480/nzd0480.xlsx
+++ b/data/nzd0480/nzd0480.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D627"/>
+  <dimension ref="A1:D630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11716,6 +11716,60 @@
         <v>344.69</v>
       </c>
       <c r="D627" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>337.82</v>
+      </c>
+      <c r="C628" t="n">
+        <v>345.77</v>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:19:51+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>337.25</v>
+      </c>
+      <c r="C629" t="n">
+        <v>345.41</v>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="n">
+        <v>336.82</v>
+      </c>
+      <c r="C630" t="n">
+        <v>345.26</v>
+      </c>
+      <c r="D630" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11732,7 +11786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B769"/>
+  <dimension ref="A1:B773"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19425,6 +19479,46 @@
       </c>
       <c r="B769" t="n">
         <v>-0.71</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B770" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B771" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B772" t="n">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B773" t="n">
+        <v>0.27</v>
       </c>
     </row>
   </sheetData>
@@ -19593,28 +19687,28 @@
         <v>0.0568</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1495779402274239</v>
+        <v>-0.1511638096898498</v>
       </c>
       <c r="J2" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="K2" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1046753965977661</v>
+        <v>0.107426313008405</v>
       </c>
       <c r="M2" t="n">
-        <v>2.512198929222538</v>
+        <v>2.507454285258835</v>
       </c>
       <c r="N2" t="n">
-        <v>9.131251329685931</v>
+        <v>9.101237435901144</v>
       </c>
       <c r="O2" t="n">
-        <v>3.021796043694202</v>
+        <v>3.016825721831002</v>
       </c>
       <c r="P2" t="n">
-        <v>342.9642425923761</v>
+        <v>342.9836804141814</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -19675,28 +19769,28 @@
         <v>0.0603</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1065022328042386</v>
+        <v>-0.1041559586727258</v>
       </c>
       <c r="J3" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="K3" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07839385713298397</v>
+        <v>0.0755822455225702</v>
       </c>
       <c r="M3" t="n">
-        <v>1.981232397048273</v>
+        <v>1.982868837031022</v>
       </c>
       <c r="N3" t="n">
-        <v>6.362679520168805</v>
+        <v>6.360453863259425</v>
       </c>
       <c r="O3" t="n">
-        <v>2.522435236070256</v>
+        <v>2.521994025222785</v>
       </c>
       <c r="P3" t="n">
-        <v>345.9061303433258</v>
+        <v>345.8773760746638</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -19738,7 +19832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D627"/>
+  <dimension ref="A1:D630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33535,6 +33629,72 @@
         </is>
       </c>
     </row>
+    <row r="628">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>-45.25779390418856,170.86287655716046</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>-45.258418359248616,170.86269303889284</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:19:51+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>-45.257792223745696,170.8628696957532</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>-45.2584172979121,170.86268870532732</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>-45.25779095604291,170.8628645196042</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>-45.25841685568851,170.86268689967505</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0480/nzd0480.xlsx
+++ b/data/nzd0480/nzd0480.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D630"/>
+  <dimension ref="A1:D634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11770,6 +11770,78 @@
         <v>345.26</v>
       </c>
       <c r="D630" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:01+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="n">
+        <v>336.3</v>
+      </c>
+      <c r="C631" t="n">
+        <v>344.81</v>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>336.24</v>
+      </c>
+      <c r="C632" t="n">
+        <v>344.8</v>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:08+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>337.26</v>
+      </c>
+      <c r="C633" t="n">
+        <v>344.8</v>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>337.21</v>
+      </c>
+      <c r="C634" t="n">
+        <v>345.07</v>
+      </c>
+      <c r="D634" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11786,7 +11858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B773"/>
+  <dimension ref="A1:B779"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19519,6 +19591,66 @@
       </c>
       <c r="B773" t="n">
         <v>0.27</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B774" t="n">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B775" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-08-11 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B776" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B777" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B778" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B779" t="n">
+        <v>-0.55</v>
       </c>
     </row>
   </sheetData>
@@ -19687,28 +19819,28 @@
         <v>0.0568</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1511638096898498</v>
+        <v>-0.1539002139993967</v>
       </c>
       <c r="J2" t="n">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="K2" t="n">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="L2" t="n">
-        <v>0.107426313008405</v>
+        <v>0.1118175039853367</v>
       </c>
       <c r="M2" t="n">
-        <v>2.507454285258835</v>
+        <v>2.504050251472907</v>
       </c>
       <c r="N2" t="n">
-        <v>9.101237435901144</v>
+        <v>9.074060529290298</v>
       </c>
       <c r="O2" t="n">
-        <v>3.016825721831002</v>
+        <v>3.012318132151765</v>
       </c>
       <c r="P2" t="n">
-        <v>342.9836804141814</v>
+        <v>343.0173108585038</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -19769,28 +19901,28 @@
         <v>0.0603</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1041559586727258</v>
+        <v>-0.1018712591879019</v>
       </c>
       <c r="J3" t="n">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="K3" t="n">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0755822455225702</v>
+        <v>0.07316737462971834</v>
       </c>
       <c r="M3" t="n">
-        <v>1.982868837031022</v>
+        <v>1.980999886944067</v>
       </c>
       <c r="N3" t="n">
-        <v>6.360453863259425</v>
+        <v>6.340419567874404</v>
       </c>
       <c r="O3" t="n">
-        <v>2.521994025222785</v>
+        <v>2.518018976869397</v>
       </c>
       <c r="P3" t="n">
-        <v>345.8773760746638</v>
+        <v>345.8492902796092</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -19832,7 +19964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D630"/>
+  <dimension ref="A1:D634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33695,6 +33827,94 @@
         </is>
       </c>
     </row>
+    <row r="631">
+      <c r="A631" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:01+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>-45.257789423006685,170.8628582600754</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>-45.258415529017554,170.86268148271844</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>-45.257789246117866,170.8628575378221</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>-45.25841549953598,170.86268136234165</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:08+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>-45.257792253227144,170.86286981612878</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>-45.25841549953598,170.86268136234165</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>-45.25779210581987,170.86286921425096</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>-45.25841629553858,170.86268461251555</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0480/nzd0480.xlsx
+++ b/data/nzd0480/nzd0480.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D634"/>
+  <dimension ref="A1:D638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11842,6 +11842,78 @@
         <v>345.07</v>
       </c>
       <c r="D634" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:13+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>335.52</v>
+      </c>
+      <c r="C635" t="n">
+        <v>344.51</v>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:20:21+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>336.02</v>
+      </c>
+      <c r="C636" t="n">
+        <v>345.17</v>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:13+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>336.69</v>
+      </c>
+      <c r="C637" t="n">
+        <v>345.49</v>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:28+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>337.01</v>
+      </c>
+      <c r="C638" t="n">
+        <v>345.07</v>
+      </c>
+      <c r="D638" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11858,7 +11930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B779"/>
+  <dimension ref="A1:B783"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19651,6 +19723,46 @@
       </c>
       <c r="B779" t="n">
         <v>-0.55</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B780" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B781" t="n">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B782" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B783" t="n">
+        <v>-0.8</v>
       </c>
     </row>
   </sheetData>
@@ -19819,28 +19931,28 @@
         <v>0.0568</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1539002139993967</v>
+        <v>-0.1571022406281638</v>
       </c>
       <c r="J2" t="n">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="K2" t="n">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1118175039853367</v>
+        <v>0.1167704493223687</v>
       </c>
       <c r="M2" t="n">
-        <v>2.504050251472907</v>
+        <v>2.502850720235681</v>
       </c>
       <c r="N2" t="n">
-        <v>9.074060529290298</v>
+        <v>9.059122492063558</v>
       </c>
       <c r="O2" t="n">
-        <v>3.012318132151765</v>
+        <v>3.009837618886368</v>
       </c>
       <c r="P2" t="n">
-        <v>343.0173108585038</v>
+        <v>343.0568219573112</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -19901,28 +20013,28 @@
         <v>0.0603</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1018712591879019</v>
+        <v>-0.09939153759326738</v>
       </c>
       <c r="J3" t="n">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="K3" t="n">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07316737462971834</v>
+        <v>0.07044847938411747</v>
       </c>
       <c r="M3" t="n">
-        <v>1.980999886944067</v>
+        <v>1.979986624981167</v>
       </c>
       <c r="N3" t="n">
-        <v>6.340419567874404</v>
+        <v>6.325303880903443</v>
       </c>
       <c r="O3" t="n">
-        <v>2.518018976869397</v>
+        <v>2.515015682039268</v>
       </c>
       <c r="P3" t="n">
-        <v>345.8492902796092</v>
+        <v>345.8186810272574</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -19964,7 +20076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D634"/>
+  <dimension ref="A1:D638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33915,6 +34027,94 @@
         </is>
       </c>
     </row>
+    <row r="635">
+      <c r="A635" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:13+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>-45.25778712345171,170.8628488707829</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>-45.258414644570124,170.8626778714142</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:20:21+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>-45.257788597525504,170.86285488956005</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>-45.25841659035435,170.8626858162837</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:13+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>-45.25779057278388,170.86286295472195</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>-45.25841753376468,170.86268966834183</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:28+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>-45.25779151619067,170.86286680673976</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>-45.25841629553858,170.86268461251555</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
